--- a/database/event/7439/event_7439_evp_summary.xlsx
+++ b/database/event/7439/event_7439_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.106</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5.8827</v>
       </c>
       <c r="D2" t="n">
         <v>3.6612</v>
@@ -545,7 +545,7 @@
         <v>7.4801</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.3542</v>
       </c>
       <c r="D3" t="n">
         <v>2.6004</v>
@@ -591,7 +591,7 @@
         <v>6.8136</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.9662</v>
       </c>
       <c r="D4" t="n">
         <v>2.3312</v>
@@ -637,7 +637,7 @@
         <v>5.7052</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.321</v>
       </c>
       <c r="D5" t="n">
         <v>1.8834</v>
@@ -683,7 +683,7 @@
         <v>4.3932</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.5573</v>
       </c>
       <c r="D6" t="n">
         <v>1.3534</v>
@@ -729,7 +729,7 @@
         <v>4.353</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="D7" t="n">
         <v>1.3372</v>
@@ -775,7 +775,7 @@
         <v>4.2496</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.4737</v>
       </c>
       <c r="D8" t="n">
         <v>1.2954</v>
@@ -821,7 +821,7 @@
         <v>3.7142</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.162</v>
       </c>
       <c r="D9" t="n">
         <v>1.0791</v>
@@ -867,7 +867,7 @@
         <v>3.2693</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.9031</v>
       </c>
       <c r="D10" t="n">
         <v>0.8994</v>
@@ -913,7 +913,7 @@
         <v>3.149</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="D11" t="n">
         <v>0.8508</v>
@@ -959,7 +959,7 @@
         <v>3.0182</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.7569</v>
       </c>
       <c r="D12" t="n">
         <v>0.7979000000000001</v>
@@ -1005,7 +1005,7 @@
         <v>2.9365</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.7093</v>
       </c>
       <c r="D13" t="n">
         <v>0.7649</v>
@@ -1051,7 +1051,7 @@
         <v>2.9188</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.699</v>
       </c>
       <c r="D14" t="n">
         <v>0.7578</v>
@@ -1097,7 +1097,7 @@
         <v>2.9107</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.6943</v>
       </c>
       <c r="D15" t="n">
         <v>0.7544999999999999</v>
@@ -1143,7 +1143,7 @@
         <v>2.8155</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.6389</v>
       </c>
       <c r="D16" t="n">
         <v>0.716</v>
@@ -1189,7 +1189,7 @@
         <v>2.6647</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.5511</v>
       </c>
       <c r="D17" t="n">
         <v>0.6551</v>
@@ -1235,7 +1235,7 @@
         <v>2.4935</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.4515</v>
       </c>
       <c r="D18" t="n">
         <v>0.586</v>
@@ -1281,7 +1281,7 @@
         <v>2.2375</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.3025</v>
       </c>
       <c r="D19" t="n">
         <v>0.4825</v>
@@ -1327,7 +1327,7 @@
         <v>2.1125</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.2297</v>
       </c>
       <c r="D20" t="n">
         <v>0.432</v>
@@ -1373,7 +1373,7 @@
         <v>2.0153</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.1731</v>
       </c>
       <c r="D21" t="n">
         <v>0.3928</v>
@@ -1419,7 +1419,7 @@
         <v>1.902</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.1072</v>
       </c>
       <c r="D22" t="n">
         <v>0.347</v>
@@ -1465,7 +1465,7 @@
         <v>1.8899</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.1001</v>
       </c>
       <c r="D23" t="n">
         <v>0.3421</v>
@@ -1511,7 +1511,7 @@
         <v>1.8232</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0613</v>
       </c>
       <c r="D24" t="n">
         <v>0.3152</v>
@@ -1557,7 +1557,7 @@
         <v>1.6816</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.9789</v>
       </c>
       <c r="D25" t="n">
         <v>0.258</v>
@@ -1603,7 +1603,7 @@
         <v>1.6567</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9644</v>
       </c>
       <c r="D26" t="n">
         <v>0.2479</v>
@@ -1649,7 +1649,7 @@
         <v>1.5754</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="D27" t="n">
         <v>0.2151</v>
@@ -1695,7 +1695,7 @@
         <v>1.4879</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8661</v>
       </c>
       <c r="D28" t="n">
         <v>0.1797</v>
@@ -1741,7 +1741,7 @@
         <v>1.4723</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="D29" t="n">
         <v>0.1734</v>
@@ -1787,7 +1787,7 @@
         <v>1.4184</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8257</v>
       </c>
       <c r="D30" t="n">
         <v>0.1516</v>
@@ -1833,7 +1833,7 @@
         <v>1.3466</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7839</v>
       </c>
       <c r="D31" t="n">
         <v>0.1226</v>
@@ -1879,7 +1879,7 @@
         <v>1.3386</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7792</v>
       </c>
       <c r="D32" t="n">
         <v>0.1194</v>
@@ -1925,7 +1925,7 @@
         <v>1.3154</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7657</v>
       </c>
       <c r="D33" t="n">
         <v>0.11</v>
@@ -1971,7 +1971,7 @@
         <v>1.3128</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.7642</v>
       </c>
       <c r="D34" t="n">
         <v>0.109</v>
@@ -2017,7 +2017,7 @@
         <v>1.2616</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>0.0883</v>
@@ -2063,7 +2063,7 @@
         <v>1.1967</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.6966</v>
       </c>
       <c r="D36" t="n">
         <v>0.0621</v>
@@ -2109,7 +2109,7 @@
         <v>1.0316</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6005</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0046</v>
@@ -2155,7 +2155,7 @@
         <v>0.9837</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5726</v>
       </c>
       <c r="D38" t="n">
         <v>-0.024</v>
@@ -2201,7 +2201,7 @@
         <v>0.9831</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.5723</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0242</v>
@@ -2247,7 +2247,7 @@
         <v>0.9074</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5282</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0548</v>
@@ -2293,7 +2293,7 @@
         <v>0.7412</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4315</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1219</v>
@@ -2339,7 +2339,7 @@
         <v>0.7213000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.4199</v>
       </c>
       <c r="D42" t="n">
         <v>-0.13</v>
@@ -2385,7 +2385,7 @@
         <v>0.5716</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3327</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1904</v>
@@ -2431,7 +2431,7 @@
         <v>0.5620000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3271</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1943</v>
@@ -2477,7 +2477,7 @@
         <v>0.5234</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3047</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2099</v>
@@ -2523,7 +2523,7 @@
         <v>0.5201</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3028</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2113</v>
@@ -2569,7 +2569,7 @@
         <v>0.432</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2515</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2468</v>
@@ -2615,7 +2615,7 @@
         <v>0.3983</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2319</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2605</v>
@@ -2661,7 +2661,7 @@
         <v>0.2352</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1369</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3263</v>
@@ -2707,7 +2707,7 @@
         <v>0.2276</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1325</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3294</v>
@@ -2753,7 +2753,7 @@
         <v>0.138</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.0803</v>
       </c>
       <c r="D51" t="n">
         <v>-0.3656</v>
@@ -2799,7 +2799,7 @@
         <v>-0.0191</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0111</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4291</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1174</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0683</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4688</v>
@@ -2891,7 +2891,7 @@
         <v>-0.1642</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.0956</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4877</v>
@@ -2937,7 +2937,7 @@
         <v>-0.1772</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1031</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4929</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2332</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1357</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5155999999999999</v>
@@ -3029,7 +3029,7 @@
         <v>-0.2352</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1369</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5164</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3006</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.175</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5427999999999999</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4093</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2383</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5867</v>
@@ -3167,7 +3167,7 @@
         <v>-0.4229</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2462</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5921999999999999</v>
@@ -3213,7 +3213,7 @@
         <v>-0.7042</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.4099</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7058</v>
@@ -3259,7 +3259,7 @@
         <v>-0.9446</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="D62" t="n">
         <v>-0.803</v>
@@ -3305,7 +3305,7 @@
         <v>-1.0382</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="D63" t="n">
         <v>-0.8408</v>
@@ -3351,7 +3351,7 @@
         <v>-1.1617</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.6762</v>
       </c>
       <c r="D64" t="n">
         <v>-0.8907</v>
@@ -3397,7 +3397,7 @@
         <v>-1.1652</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.6783</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8921</v>
@@ -3443,7 +3443,7 @@
         <v>-1.234</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.7183</v>
       </c>
       <c r="D66" t="n">
         <v>-0.9199000000000001</v>
@@ -3489,7 +3489,7 @@
         <v>-1.2748</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.7421</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9364</v>
@@ -3535,7 +3535,7 @@
         <v>-1.3587</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.7909</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9702</v>
@@ -3581,7 +3581,7 @@
         <v>-1.4462</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.8418</v>
       </c>
       <c r="D69" t="n">
         <v>-1.0056</v>
@@ -3627,7 +3627,7 @@
         <v>-1.5521</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.9035</v>
       </c>
       <c r="D70" t="n">
         <v>-1.0484</v>
@@ -3673,7 +3673,7 @@
         <v>-1.6026</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.9329</v>
       </c>
       <c r="D71" t="n">
         <v>-1.0688</v>
@@ -3719,7 +3719,7 @@
         <v>-1.6107</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.9376</v>
       </c>
       <c r="D72" t="n">
         <v>-1.072</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6275</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.9474</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0788</v>
@@ -3811,7 +3811,7 @@
         <v>-1.656</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.964</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0903</v>
@@ -3857,7 +3857,7 @@
         <v>-1.8113</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.0544</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1531</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9144</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.1144</v>
       </c>
       <c r="D76" t="n">
         <v>-1.1947</v>
@@ -3949,7 +3949,7 @@
         <v>-2.1546</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.2542</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2918</v>
@@ -3995,7 +3995,7 @@
         <v>-2.21</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.2864</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3142</v>
@@ -4041,7 +4041,7 @@
         <v>-2.4976</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.4539</v>
       </c>
       <c r="D79" t="n">
         <v>-1.4303</v>
@@ -4087,7 +4087,7 @@
         <v>-3.5057</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.0407</v>
       </c>
       <c r="D80" t="n">
         <v>-1.8376</v>
@@ -4133,7 +4133,7 @@
         <v>-4.6117</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.6845</v>
       </c>
       <c r="D81" t="n">
         <v>-2.2844</v>

--- a/database/event/7439/event_7439_evp_summary.xlsx
+++ b/database/event/7439/event_7439_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.106</v>
+        <v>10.3355</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8827</v>
+        <v>6.0163</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6612</v>
+        <v>3.6738</v>
       </c>
       <c r="E2" t="n">
-        <v>10.106</v>
+        <v>10.3355</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7356</v>
+        <v>4.9651</v>
       </c>
       <c r="G2" t="n">
         <v>5.3704</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1224</v>
+        <v>5.4822</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1942</v>
+        <v>5.6218</v>
       </c>
       <c r="J2" t="n">
         <v>5.3704</v>
@@ -529,7 +529,7 @@
         <v>181</v>
       </c>
       <c r="M2" t="n">
-        <v>10.5646</v>
+        <v>10.9922</v>
       </c>
       <c r="N2" t="n">
         <v>388</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4801</v>
+        <v>7.735</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3542</v>
+        <v>4.5026</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6004</v>
+        <v>2.6377</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4801</v>
+        <v>7.735</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0209</v>
+        <v>2.2758</v>
       </c>
       <c r="G3" t="n">
         <v>5.4592</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0209</v>
+        <v>2.2758</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0209</v>
+        <v>2.2758</v>
       </c>
       <c r="J3" t="n">
         <v>5.4592</v>
@@ -575,7 +575,7 @@
         <v>194</v>
       </c>
       <c r="M3" t="n">
-        <v>7.4801</v>
+        <v>7.734999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>308</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8136</v>
+        <v>7.7204</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9662</v>
+        <v>4.4941</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3312</v>
+        <v>2.6319</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8136</v>
+        <v>7.7204</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1129</v>
+        <v>3.0198</v>
       </c>
       <c r="G4" t="n">
         <v>4.7007</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1129</v>
+        <v>3.0198</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1129</v>
+        <v>3.0198</v>
       </c>
       <c r="J4" t="n">
         <v>4.7007</v>
@@ -621,7 +621,7 @@
         <v>194</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8136</v>
+        <v>7.7205</v>
       </c>
       <c r="N4" t="n">
         <v>308</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7052</v>
+        <v>6.3683</v>
       </c>
       <c r="C5" t="n">
-        <v>3.321</v>
+        <v>3.707</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8834</v>
+        <v>2.0932</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7052</v>
+        <v>6.3683</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5939</v>
+        <v>2.257</v>
       </c>
       <c r="G5" t="n">
         <v>4.1113</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5939</v>
+        <v>2.257</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5939</v>
+        <v>2.257</v>
       </c>
       <c r="J5" t="n">
         <v>4.1113</v>
@@ -667,7 +667,7 @@
         <v>194</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7052</v>
+        <v>6.3683</v>
       </c>
       <c r="N5" t="n">
         <v>308</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3932</v>
+        <v>5.0543</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5573</v>
+        <v>2.9421</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3534</v>
+        <v>1.5697</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3932</v>
+        <v>5.0543</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8663</v>
+        <v>3.8125</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4731</v>
+        <v>1.2418</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6501</v>
+        <v>3.8125</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2006</v>
+        <v>3.8125</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4731</v>
+        <v>1.2418</v>
       </c>
       <c r="K6" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7275</v>
+        <v>5.0543</v>
       </c>
       <c r="N6" t="n">
-        <v>149</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.353</v>
+        <v>4.3932</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5339</v>
+        <v>2.5573</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3372</v>
+        <v>1.3063</v>
       </c>
       <c r="E7" t="n">
-        <v>4.353</v>
+        <v>4.3932</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5415</v>
+        <v>4.8663</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8115</v>
+        <v>-0.4731</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5415</v>
+        <v>8.215299999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8705</v>
+        <v>6.6587</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8115</v>
+        <v>-0.4731</v>
       </c>
       <c r="K7" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L7" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="M7" t="n">
-        <v>3.682</v>
+        <v>6.1856</v>
       </c>
       <c r="N7" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2496</v>
+        <v>4.353</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4737</v>
+        <v>2.5339</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2954</v>
+        <v>1.2903</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2496</v>
+        <v>4.353</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0078</v>
+        <v>3.5415</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2418</v>
+        <v>0.8115</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0078</v>
+        <v>3.5415</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0078</v>
+        <v>2.8705</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2418</v>
+        <v>0.8115</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="L8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2496</v>
+        <v>3.682</v>
       </c>
       <c r="N8" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9">
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7142</v>
+        <v>3.6929</v>
       </c>
       <c r="C9" t="n">
-        <v>2.162</v>
+        <v>2.1496</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0791</v>
+        <v>1.0273</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7142</v>
+        <v>3.6929</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9118</v>
+        <v>1.8905</v>
       </c>
       <c r="G9" t="n">
         <v>1.8024</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9118</v>
+        <v>1.8905</v>
       </c>
       <c r="I9" t="n">
         <v>1.9386</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2693</v>
+        <v>3.4759</v>
       </c>
       <c r="C10" t="n">
-        <v>1.9031</v>
+        <v>2.0233</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8994</v>
+        <v>0.9409</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2693</v>
+        <v>3.4759</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2693</v>
+        <v>4.0792</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6158</v>
+        <v>4.0792</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7412</v>
+        <v>3.3063</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>107</v>
@@ -897,7 +897,7 @@
         <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7412</v>
+        <v>2.703</v>
       </c>
       <c r="N10" t="n">
         <v>178</v>
@@ -906,231 +906,231 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.149</v>
+        <v>3.2878</v>
       </c>
       <c r="C11" t="n">
-        <v>1.833</v>
+        <v>1.9138</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8508</v>
+        <v>0.8659</v>
       </c>
       <c r="E11" t="n">
-        <v>3.149</v>
+        <v>3.2878</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6686</v>
+        <v>4.2878</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4804</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6686</v>
+        <v>4.6901</v>
       </c>
       <c r="I11" t="n">
-        <v>2.706</v>
+        <v>3.8015</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4804</v>
+        <v>-1</v>
       </c>
       <c r="K11" t="n">
-        <v>177</v>
+        <v>107</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1864</v>
+        <v>2.8015</v>
       </c>
       <c r="N11" t="n">
-        <v>218</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0182</v>
+        <v>3.1249</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7569</v>
+        <v>1.819</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.8011</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0182</v>
+        <v>3.1249</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0182</v>
+        <v>2.6445</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.4804</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0182</v>
+        <v>2.6445</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0463</v>
+        <v>2.7119</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.4804</v>
       </c>
       <c r="K12" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0463</v>
+        <v>3.1923</v>
       </c>
       <c r="N12" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9365</v>
+        <v>3.0351</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7093</v>
+        <v>1.7667</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7649</v>
+        <v>0.7653</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9365</v>
+        <v>3.0351</v>
       </c>
       <c r="F13" t="n">
-        <v>0.525</v>
+        <v>2.402</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4115</v>
+        <v>0.6331</v>
       </c>
       <c r="H13" t="n">
-        <v>0.525</v>
+        <v>2.402</v>
       </c>
       <c r="I13" t="n">
-        <v>0.525</v>
+        <v>2.4631</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4115</v>
+        <v>0.6331</v>
       </c>
       <c r="K13" t="n">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="L13" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9365</v>
+        <v>3.0962</v>
       </c>
       <c r="N13" t="n">
-        <v>308</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9188</v>
+        <v>2.9957</v>
       </c>
       <c r="C14" t="n">
-        <v>1.699</v>
+        <v>1.7438</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7578</v>
+        <v>0.7496</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9188</v>
+        <v>2.9957</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2857</v>
+        <v>2.9957</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6331</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2857</v>
+        <v>2.9957</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3178</v>
+        <v>3.0463</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6331</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="L14" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9509</v>
+        <v>3.0463</v>
       </c>
       <c r="N14" t="n">
-        <v>388</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9107</v>
+        <v>2.9365</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6943</v>
+        <v>1.7093</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.726</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9107</v>
+        <v>2.9365</v>
       </c>
       <c r="F15" t="n">
-        <v>3.514</v>
+        <v>0.525</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6032999999999999</v>
+        <v>2.4115</v>
       </c>
       <c r="H15" t="n">
-        <v>3.514</v>
+        <v>0.525</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8482</v>
+        <v>0.525</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6032999999999999</v>
+        <v>2.4115</v>
       </c>
       <c r="K15" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2449</v>
+        <v>2.9365</v>
       </c>
       <c r="N15" t="n">
-        <v>178</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16">
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8155</v>
+        <v>2.8095</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6389</v>
+        <v>1.6354</v>
       </c>
       <c r="D16" t="n">
-        <v>0.716</v>
+        <v>0.6754</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8155</v>
+        <v>2.8095</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5324</v>
+        <v>0.5265</v>
       </c>
       <c r="G16" t="n">
         <v>2.283</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5324</v>
+        <v>0.5265</v>
       </c>
       <c r="I16" t="n">
         <v>0.5399</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6647</v>
+        <v>2.6449</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5511</v>
+        <v>1.5396</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6551</v>
+        <v>0.6098</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6647</v>
+        <v>2.6449</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6647</v>
+        <v>2.6449</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6647</v>
+        <v>2.6449</v>
       </c>
       <c r="I17" t="n">
         <v>2.6896</v>
@@ -1238,7 +1238,7 @@
         <v>1.4515</v>
       </c>
       <c r="D18" t="n">
-        <v>0.586</v>
+        <v>0.5495</v>
       </c>
       <c r="E18" t="n">
         <v>2.4935</v>
@@ -1284,7 +1284,7 @@
         <v>1.3025</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4825</v>
+        <v>0.4475</v>
       </c>
       <c r="E19" t="n">
         <v>2.2375</v>
@@ -1320,323 +1320,323 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1125</v>
+        <v>2.1822</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2297</v>
+        <v>1.2703</v>
       </c>
       <c r="D20" t="n">
-        <v>0.432</v>
+        <v>0.4255</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1125</v>
+        <v>2.1822</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2031</v>
+        <v>2.1822</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0906</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2031</v>
+        <v>2.1822</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7857</v>
+        <v>2.1822</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0906</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>117</v>
       </c>
       <c r="L20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6951</v>
+        <v>2.1822</v>
       </c>
       <c r="N20" t="n">
-        <v>149</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0153</v>
+        <v>2.1125</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1731</v>
+        <v>1.2297</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3928</v>
+        <v>0.3977</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0153</v>
+        <v>2.1125</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0153</v>
+        <v>2.2031</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.0906</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0153</v>
+        <v>2.2031</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0153</v>
+        <v>1.7857</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.0906</v>
       </c>
       <c r="K21" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0153</v>
+        <v>1.6951</v>
       </c>
       <c r="N21" t="n">
-        <v>123</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.902</v>
+        <v>2.0459</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1072</v>
+        <v>1.1909</v>
       </c>
       <c r="D22" t="n">
-        <v>0.347</v>
+        <v>0.3712</v>
       </c>
       <c r="E22" t="n">
-        <v>1.902</v>
+        <v>2.0459</v>
       </c>
       <c r="F22" t="n">
-        <v>1.902</v>
+        <v>2.0459</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.902</v>
+        <v>2.0459</v>
       </c>
       <c r="I22" t="n">
-        <v>1.902</v>
+        <v>2.0459</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.902</v>
+        <v>2.0459</v>
       </c>
       <c r="N22" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8899</v>
+        <v>2.0166</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1001</v>
+        <v>1.1739</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3421</v>
+        <v>0.3595</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8899</v>
+        <v>2.0166</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8899</v>
+        <v>2.0166</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8899</v>
+        <v>2.0166</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8899</v>
+        <v>2.0166</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8899</v>
+        <v>2.0166</v>
       </c>
       <c r="N23" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8232</v>
+        <v>1.902</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0613</v>
+        <v>1.1072</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3152</v>
+        <v>0.3138</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8232</v>
+        <v>1.902</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3213</v>
+        <v>1.902</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4981</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3213</v>
+        <v>1.902</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8815</v>
+        <v>1.902</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4981</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3834</v>
+        <v>1.902</v>
       </c>
       <c r="N24" t="n">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6816</v>
+        <v>1.8899</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9789</v>
+        <v>1.1001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.258</v>
+        <v>0.309</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6816</v>
+        <v>1.8899</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6816</v>
+        <v>1.8899</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6816</v>
+        <v>1.8899</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6816</v>
+        <v>1.8899</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6816</v>
+        <v>1.8899</v>
       </c>
       <c r="N25" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6567</v>
+        <v>1.8232</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9644</v>
+        <v>1.0613</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2479</v>
+        <v>0.2825</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6567</v>
+        <v>1.8232</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6567</v>
+        <v>2.3213</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.4981</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6567</v>
+        <v>2.3213</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6721</v>
+        <v>1.8815</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.4981</v>
       </c>
       <c r="K26" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6721</v>
+        <v>1.3834</v>
       </c>
       <c r="N26" t="n">
-        <v>201</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5754</v>
+        <v>1.6686</v>
       </c>
       <c r="C27" t="n">
-        <v>0.917</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2151</v>
+        <v>0.2209</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5754</v>
+        <v>1.6686</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5754</v>
+        <v>1.6686</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5754</v>
+        <v>1.6686</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5754</v>
+        <v>1.6686</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.5754</v>
+        <v>1.6686</v>
       </c>
       <c r="N27" t="n">
         <v>123</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4879</v>
+        <v>1.6443</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8661</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1797</v>
+        <v>0.2112</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4879</v>
+        <v>1.6443</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4879</v>
+        <v>1.6443</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4879</v>
+        <v>1.6443</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4879</v>
+        <v>1.6721</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4879</v>
+        <v>1.6721</v>
       </c>
       <c r="N28" t="n">
-        <v>145</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4723</v>
+        <v>1.5466</v>
       </c>
       <c r="C29" t="n">
-        <v>0.857</v>
+        <v>0.9003</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1734</v>
+        <v>0.1723</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4723</v>
+        <v>1.5466</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8109</v>
+        <v>1.8852</v>
       </c>
       <c r="G29" t="n">
         <v>-0.3386</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8109</v>
+        <v>1.8852</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4678</v>
+        <v>1.528</v>
       </c>
       <c r="J29" t="n">
         <v>-0.3386</v>
@@ -1771,7 +1771,7 @@
         <v>71</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1292</v>
+        <v>1.1894</v>
       </c>
       <c r="N29" t="n">
         <v>178</v>
@@ -1780,219 +1780,219 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4184</v>
+        <v>1.5439</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8257</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1516</v>
+        <v>0.1712</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4184</v>
+        <v>1.5439</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4184</v>
+        <v>1.5439</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4184</v>
+        <v>1.5439</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4184</v>
+        <v>1.5439</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4184</v>
+        <v>1.5439</v>
       </c>
       <c r="N30" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3466</v>
+        <v>1.5218</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7839</v>
+        <v>0.8858</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1226</v>
+        <v>0.1624</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3466</v>
+        <v>1.5218</v>
       </c>
       <c r="F31" t="n">
-        <v>1.9617</v>
+        <v>1.5218</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6151</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.9617</v>
+        <v>1.5218</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9892</v>
+        <v>1.5218</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6151</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="L31" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3741</v>
+        <v>1.5218</v>
       </c>
       <c r="N31" t="n">
-        <v>218</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3386</v>
+        <v>1.4879</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7792</v>
+        <v>0.8661</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1194</v>
+        <v>0.1489</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3386</v>
+        <v>1.4879</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3386</v>
+        <v>1.4879</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3386</v>
+        <v>1.4879</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3386</v>
+        <v>1.4879</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3386</v>
+        <v>1.4879</v>
       </c>
       <c r="N32" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3154</v>
+        <v>1.4184</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7657</v>
+        <v>0.8257</v>
       </c>
       <c r="D33" t="n">
-        <v>0.11</v>
+        <v>0.1212</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3154</v>
+        <v>1.4184</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3154</v>
+        <v>1.4184</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3154</v>
+        <v>1.4184</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3154</v>
+        <v>1.4184</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3154</v>
+        <v>1.4184</v>
       </c>
       <c r="N33" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3128</v>
+        <v>1.3247</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7642</v>
+        <v>0.7711</v>
       </c>
       <c r="D34" t="n">
-        <v>0.109</v>
+        <v>0.0839</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3128</v>
+        <v>1.3247</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9773</v>
+        <v>1.9398</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6645</v>
+        <v>-0.6151</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9773</v>
+        <v>1.9398</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0051</v>
+        <v>1.9892</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6645</v>
+        <v>-0.6151</v>
       </c>
       <c r="K34" t="n">
         <v>177</v>
@@ -2001,7 +2001,7 @@
         <v>41</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3406</v>
+        <v>1.3741</v>
       </c>
       <c r="N34" t="n">
         <v>218</v>
@@ -2010,185 +2010,185 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2616</v>
+        <v>1.3097</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7624</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0883</v>
+        <v>0.0779</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2616</v>
+        <v>1.3097</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2616</v>
+        <v>1.3097</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2616</v>
+        <v>1.3097</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2616</v>
+        <v>1.3097</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2616</v>
+        <v>1.3097</v>
       </c>
       <c r="N35" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1967</v>
+        <v>1.2908</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6966</v>
+        <v>0.7514</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0621</v>
+        <v>0.0703</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1967</v>
+        <v>1.2908</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1967</v>
+        <v>1.9553</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.6645</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1967</v>
+        <v>1.9553</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1967</v>
+        <v>2.0051</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.6645</v>
       </c>
       <c r="K36" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1967</v>
+        <v>1.3406</v>
       </c>
       <c r="N36" t="n">
-        <v>172</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.0316</v>
+        <v>1.2616</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6005</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0046</v>
+        <v>0.0587</v>
       </c>
       <c r="E37" t="n">
-        <v>1.0316</v>
+        <v>1.2616</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0316</v>
+        <v>1.2616</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.0316</v>
+        <v>1.2616</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0316</v>
+        <v>1.2616</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.0316</v>
+        <v>1.2616</v>
       </c>
       <c r="N37" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9837</v>
+        <v>1.0165</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5726</v>
+        <v>0.5917</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.024</v>
+        <v>-0.0389</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9837</v>
+        <v>1.0165</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9837</v>
+        <v>1.0557</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.0392</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9837</v>
+        <v>1.0557</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9929</v>
+        <v>1.0557</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.0392</v>
       </c>
       <c r="K38" t="n">
-        <v>201</v>
+        <v>115</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9929</v>
+        <v>1.0165</v>
       </c>
       <c r="N38" t="n">
-        <v>201</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39">
@@ -2204,7 +2204,7 @@
         <v>0.5723</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0242</v>
+        <v>-0.0522</v>
       </c>
       <c r="E39" t="n">
         <v>0.9831</v>
@@ -2240,81 +2240,81 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9074</v>
+        <v>0.9764</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5282</v>
+        <v>0.5684</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0548</v>
+        <v>-0.0549</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9074</v>
+        <v>0.9764</v>
       </c>
       <c r="F40" t="n">
-        <v>0.576</v>
+        <v>0.9764</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3314</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.576</v>
+        <v>0.9764</v>
       </c>
       <c r="I40" t="n">
-        <v>0.576</v>
+        <v>0.9929</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3314</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L40" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9074</v>
+        <v>0.9929</v>
       </c>
       <c r="N40" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7412</v>
+        <v>0.9074</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4315</v>
+        <v>0.5282</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1219</v>
+        <v>-0.0824</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7412</v>
+        <v>0.9074</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7804</v>
+        <v>0.576</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0392</v>
+        <v>0.3314</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7804</v>
+        <v>0.576</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7804</v>
+        <v>0.576</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0392</v>
+        <v>0.3314</v>
       </c>
       <c r="K41" t="n">
         <v>115</v>
@@ -2323,7 +2323,7 @@
         <v>67</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7412</v>
+        <v>0.9074</v>
       </c>
       <c r="N41" t="n">
         <v>182</v>
@@ -2332,93 +2332,93 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4199</v>
+        <v>0.5231</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.13</v>
+        <v>-0.0859</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5716</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3327</v>
+        <v>0.4199</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1904</v>
+        <v>-0.1565</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5716</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5716</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5716</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5716</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5716</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
@@ -2434,7 +2434,7 @@
         <v>0.3271</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1943</v>
+        <v>-0.22</v>
       </c>
       <c r="E44" t="n">
         <v>0.5620000000000001</v>
@@ -2480,7 +2480,7 @@
         <v>0.3047</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2099</v>
+        <v>-0.2354</v>
       </c>
       <c r="E45" t="n">
         <v>0.5234</v>
@@ -2526,7 +2526,7 @@
         <v>0.3028</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2113</v>
+        <v>-0.2367</v>
       </c>
       <c r="E46" t="n">
         <v>0.5201</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.432</v>
+        <v>0.4192</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2515</v>
+        <v>0.244</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2468</v>
+        <v>-0.2769</v>
       </c>
       <c r="E47" t="n">
-        <v>0.432</v>
+        <v>0.4192</v>
       </c>
       <c r="F47" t="n">
-        <v>1.1519</v>
+        <v>1.1391</v>
       </c>
       <c r="G47" t="n">
         <v>-0.7199</v>
       </c>
       <c r="H47" t="n">
-        <v>1.1519</v>
+        <v>1.1391</v>
       </c>
       <c r="I47" t="n">
         <v>1.1681</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3983</v>
+        <v>0.394</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2319</v>
+        <v>0.2293</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2605</v>
+        <v>-0.2869</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3983</v>
+        <v>0.394</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3853</v>
+        <v>0.381</v>
       </c>
       <c r="G48" t="n">
         <v>0.013</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3853</v>
+        <v>0.381</v>
       </c>
       <c r="I48" t="n">
         <v>0.3907</v>
@@ -2654,231 +2654,231 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2352</v>
+        <v>0.3757</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1369</v>
+        <v>0.2187</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3263</v>
+        <v>-0.2942</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2352</v>
+        <v>0.3757</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2352</v>
+        <v>-0.1331</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.5088</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2352</v>
+        <v>-0.1331</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2352</v>
+        <v>-0.1331</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.5088</v>
       </c>
       <c r="K49" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2352</v>
+        <v>0.3757</v>
       </c>
       <c r="N49" t="n">
-        <v>85</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2276</v>
+        <v>0.2352</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1325</v>
+        <v>0.1369</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3294</v>
+        <v>-0.3502</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2276</v>
+        <v>0.2352</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2276</v>
+        <v>0.2352</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2276</v>
+        <v>0.2352</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2276</v>
+        <v>0.2352</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2276</v>
+        <v>0.2352</v>
       </c>
       <c r="N50" t="n">
-        <v>117</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.138</v>
+        <v>0.2276</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0803</v>
+        <v>0.1325</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3656</v>
+        <v>-0.3532</v>
       </c>
       <c r="E51" t="n">
-        <v>0.138</v>
+        <v>0.2276</v>
       </c>
       <c r="F51" t="n">
-        <v>0.138</v>
+        <v>0.2276</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.138</v>
+        <v>0.2276</v>
       </c>
       <c r="I51" t="n">
-        <v>0.138</v>
+        <v>0.2276</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.138</v>
+        <v>0.2276</v>
       </c>
       <c r="N51" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0191</v>
+        <v>0.138</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0111</v>
+        <v>0.0803</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4291</v>
+        <v>-0.3889</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0191</v>
+        <v>0.138</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0191</v>
+        <v>0.138</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0191</v>
+        <v>0.138</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0191</v>
+        <v>0.138</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0191</v>
+        <v>0.138</v>
       </c>
       <c r="N52" t="n">
-        <v>96</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1174</v>
+        <v>-0.0191</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0683</v>
+        <v>-0.0111</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4688</v>
+        <v>-0.4515</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1174</v>
+        <v>-0.0191</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5813</v>
+        <v>-0.0191</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.6987</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5813</v>
+        <v>-0.0191</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4712</v>
+        <v>-0.0191</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.6987</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="L53" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2275</v>
+        <v>-0.0191</v>
       </c>
       <c r="N53" t="n">
-        <v>149</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1642</v>
+        <v>-0.1029</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0956</v>
+        <v>-0.0599</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4877</v>
+        <v>-0.4849</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1642</v>
+        <v>-0.1029</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1642</v>
+        <v>-0.1029</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1642</v>
+        <v>-0.1029</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1642</v>
+        <v>-0.1029</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1642</v>
+        <v>-0.1029</v>
       </c>
       <c r="N54" t="n">
         <v>59</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1772</v>
+        <v>-0.1174</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1031</v>
+        <v>-0.0683</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4929</v>
+        <v>-0.4907</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1772</v>
+        <v>-0.1174</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1772</v>
+        <v>0.5813</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.6987</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1772</v>
+        <v>0.5813</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1772</v>
+        <v>0.4712</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.6987</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1772</v>
+        <v>-0.2275</v>
       </c>
       <c r="N55" t="n">
-        <v>96</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2332</v>
+        <v>-0.1772</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1357</v>
+        <v>-0.1031</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5145</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2332</v>
+        <v>-0.1772</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.742</v>
+        <v>-0.1772</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5088</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.742</v>
+        <v>-0.1772</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.742</v>
+        <v>-0.1772</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5088</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="L56" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2332</v>
+        <v>-0.1772</v>
       </c>
       <c r="N56" t="n">
-        <v>182</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57">
@@ -3032,7 +3032,7 @@
         <v>-0.1369</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5164</v>
+        <v>-0.5376</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2352</v>
@@ -3078,7 +3078,7 @@
         <v>-0.175</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5637</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3006</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2383</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5867</v>
+        <v>-0.607</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4093</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2462</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4229</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4099</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7058</v>
+        <v>-0.7245</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7042</v>
@@ -3262,7 +3262,7 @@
         <v>-0.5499000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.803</v>
+        <v>-0.8202</v>
       </c>
       <c r="E62" t="n">
         <v>-0.9446</v>
@@ -3308,7 +3308,7 @@
         <v>-0.6042999999999999</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8408</v>
+        <v>-0.8575</v>
       </c>
       <c r="E63" t="n">
         <v>-1.0382</v>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1617</v>
+        <v>-1.1569</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.6762</v>
+        <v>-0.6734</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8907</v>
+        <v>-0.9048</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.1617</v>
+        <v>-1.1569</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.1617</v>
+        <v>-1.1569</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.1617</v>
+        <v>-1.1569</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.1617</v>
+        <v>-1.1569</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-1.1617</v>
+        <v>-1.1569</v>
       </c>
       <c r="N64" t="n">
         <v>117</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6783</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8921</v>
+        <v>-0.9081</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1652</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.234</v>
+        <v>-1.2317</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.7183</v>
+        <v>-0.717</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.9346</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.234</v>
+        <v>-1.2317</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.234</v>
+        <v>-0.2317</v>
       </c>
       <c r="G66" t="n">
         <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.234</v>
+        <v>-0.2317</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1897</v>
+        <v>-0.1878</v>
       </c>
       <c r="J66" t="n">
         <v>-1</v>
@@ -3473,7 +3473,7 @@
         <v>32</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.1897</v>
+        <v>-1.1878</v>
       </c>
       <c r="N66" t="n">
         <v>149</v>
@@ -3492,7 +3492,7 @@
         <v>-0.7421</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9364</v>
+        <v>-0.9518</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2748</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7909</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9702</v>
+        <v>-0.9852</v>
       </c>
       <c r="E68" t="n">
         <v>-1.3587</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8418</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0056</v>
+        <v>-1.0201</v>
       </c>
       <c r="E69" t="n">
         <v>-1.4462</v>
@@ -3630,7 +3630,7 @@
         <v>-0.9035</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0484</v>
+        <v>-1.0623</v>
       </c>
       <c r="E70" t="n">
         <v>-1.5521</v>
@@ -3676,7 +3676,7 @@
         <v>-0.9329</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0688</v>
+        <v>-1.0824</v>
       </c>
       <c r="E71" t="n">
         <v>-1.6026</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9376</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.072</v>
+        <v>-1.0856</v>
       </c>
       <c r="E72" t="n">
         <v>-1.6107</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9474</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0788</v>
+        <v>-1.0923</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6275</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.656</v>
+        <v>-1.6496</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.964</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0903</v>
+        <v>-1.1011</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.656</v>
+        <v>-1.6496</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6973</v>
+        <v>-0.6909</v>
       </c>
       <c r="G74" t="n">
         <v>-0.9587</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6973</v>
+        <v>-0.6909</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.6973</v>
+        <v>-0.6909</v>
       </c>
       <c r="J74" t="n">
         <v>-0.9587</v>
@@ -3841,7 +3841,7 @@
         <v>194</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.656</v>
+        <v>-1.6496</v>
       </c>
       <c r="N74" t="n">
         <v>308</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0544</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1531</v>
+        <v>-1.1655</v>
       </c>
       <c r="E75" t="n">
         <v>-1.8113</v>
@@ -3906,7 +3906,7 @@
         <v>-1.1144</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1947</v>
+        <v>-1.2066</v>
       </c>
       <c r="E76" t="n">
         <v>-1.9144</v>
@@ -3952,7 +3952,7 @@
         <v>-1.2542</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2918</v>
+        <v>-1.3023</v>
       </c>
       <c r="E77" t="n">
         <v>-2.1546</v>
@@ -3998,7 +3998,7 @@
         <v>-1.2864</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3142</v>
+        <v>-1.3244</v>
       </c>
       <c r="E78" t="n">
         <v>-2.21</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4539</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4303</v>
+        <v>-1.439</v>
       </c>
       <c r="E79" t="n">
         <v>-2.4976</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.5057</v>
+        <v>-3.4796</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.0407</v>
+        <v>-2.0255</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8376</v>
+        <v>-1.8302</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.5057</v>
+        <v>-3.4796</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.5057</v>
+        <v>-3.4796</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.5057</v>
+        <v>-3.4796</v>
       </c>
       <c r="I80" t="n">
         <v>-3.5384</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.6117</v>
+        <v>-4.5879</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.6845</v>
+        <v>-2.6706</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2844</v>
+        <v>-2.2717</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.6117</v>
+        <v>-4.5879</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1364</v>
+        <v>-2.1126</v>
       </c>
       <c r="G81" t="n">
         <v>-2.4753</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1364</v>
+        <v>-2.1126</v>
       </c>
       <c r="I81" t="n">
         <v>-2.1664</v>

--- a/database/event/7439/event_7439_evp_summary.xlsx
+++ b/database/event/7439/event_7439_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.761100000000001</v>
+        <v>8.7865</v>
       </c>
       <c r="C2" t="n">
-        <v>5.0999</v>
+        <v>5.1146</v>
       </c>
       <c r="D2" t="n">
-        <v>3.364</v>
+        <v>3.3109</v>
       </c>
       <c r="E2" t="n">
-        <v>8.761100000000001</v>
+        <v>8.7865</v>
       </c>
       <c r="F2" t="n">
         <v>3.6978</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9296</v>
+        <v>7.049</v>
       </c>
       <c r="C3" t="n">
-        <v>4.0337</v>
+        <v>4.1032</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5303</v>
+        <v>2.5348</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9296</v>
+        <v>7.049</v>
       </c>
       <c r="F3" t="n">
         <v>2.2575</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9261</v>
+        <v>6.9698</v>
       </c>
       <c r="C4" t="n">
-        <v>4.0317</v>
+        <v>4.0571</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5287</v>
+        <v>2.4994</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9261</v>
+        <v>6.9698</v>
       </c>
       <c r="F4" t="n">
         <v>2.6272</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6508</v>
+        <v>6.8659</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8715</v>
+        <v>3.9967</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4034</v>
+        <v>2.453</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6508</v>
+        <v>6.8659</v>
       </c>
       <c r="F5" t="n">
         <v>2.4293</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8976</v>
+        <v>5.3414</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8509</v>
+        <v>3.1092</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6053</v>
+        <v>1.7721</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8976</v>
+        <v>5.3414</v>
       </c>
       <c r="F6" t="n">
         <v>3.714</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1827</v>
+        <v>4.4056</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4348</v>
+        <v>2.5645</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2798</v>
+        <v>1.3541</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1827</v>
+        <v>4.4056</v>
       </c>
       <c r="F7" t="n">
-        <v>2.164</v>
+        <v>4.5807</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0187</v>
+        <v>-0.4175</v>
       </c>
       <c r="H7" t="n">
-        <v>2.164</v>
+        <v>13.5593</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3356</v>
+        <v>7.3219</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0187</v>
+        <v>-0.4175</v>
       </c>
       <c r="K7" t="n">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="L7" t="n">
-        <v>181</v>
+        <v>32</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3543</v>
+        <v>6.904400000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>388</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1632</v>
+        <v>4.2768</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4234</v>
+        <v>2.4895</v>
       </c>
       <c r="D8" t="n">
-        <v>1.271</v>
+        <v>1.2965</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1632</v>
+        <v>4.2768</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5807</v>
+        <v>2.164</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4175</v>
+        <v>2.0187</v>
       </c>
       <c r="H8" t="n">
-        <v>13.5593</v>
+        <v>2.164</v>
       </c>
       <c r="I8" t="n">
-        <v>7.3219</v>
+        <v>2.3356</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4175</v>
+        <v>2.0187</v>
       </c>
       <c r="K8" t="n">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="M8" t="n">
-        <v>6.904400000000001</v>
+        <v>4.3543</v>
       </c>
       <c r="N8" t="n">
-        <v>149</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.822</v>
+        <v>4.0546</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2248</v>
+        <v>2.3602</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1156</v>
+        <v>1.1973</v>
       </c>
       <c r="E9" t="n">
-        <v>3.822</v>
+        <v>4.0546</v>
       </c>
       <c r="F9" t="n">
         <v>3.1447</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7762</v>
+        <v>3.8781</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1981</v>
+        <v>2.2575</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0948</v>
+        <v>1.1184</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7762</v>
+        <v>3.8781</v>
       </c>
       <c r="F10" t="n">
         <v>1.2387</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6009</v>
+        <v>3.6092</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0961</v>
+        <v>2.1009</v>
       </c>
       <c r="D11" t="n">
-        <v>1.015</v>
+        <v>0.9983</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6009</v>
+        <v>3.6092</v>
       </c>
       <c r="F11" t="n">
         <v>1.2319</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3196</v>
+        <v>3.3877</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9323</v>
+        <v>1.972</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8869</v>
+        <v>0.8994</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3196</v>
+        <v>3.3877</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5843</v>
+        <v>3.653</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7353</v>
+        <v>-0.3602</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9312</v>
+        <v>7.1583</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1637</v>
+        <v>3.8654</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7353</v>
+        <v>-0.3602</v>
       </c>
       <c r="K12" t="n">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="L12" t="n">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>3.899</v>
+        <v>3.5052</v>
       </c>
       <c r="N12" t="n">
-        <v>388</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2928</v>
+        <v>3.3396</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9167</v>
+        <v>1.944</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8747</v>
+        <v>0.8779</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2928</v>
+        <v>3.3396</v>
       </c>
       <c r="F13" t="n">
-        <v>3.653</v>
+        <v>2.5843</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3602</v>
+        <v>0.7353</v>
       </c>
       <c r="H13" t="n">
-        <v>7.1583</v>
+        <v>2.9312</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8654</v>
+        <v>3.1637</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3602</v>
+        <v>0.7353</v>
       </c>
       <c r="K13" t="n">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="L13" t="n">
-        <v>71</v>
+        <v>181</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5052</v>
+        <v>3.899</v>
       </c>
       <c r="N13" t="n">
-        <v>178</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1369</v>
+        <v>3.2414</v>
       </c>
       <c r="C14" t="n">
-        <v>1.826</v>
+        <v>1.8868</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8038</v>
+        <v>0.834</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1369</v>
+        <v>3.2414</v>
       </c>
       <c r="F14" t="n">
         <v>2.6709</v>
@@ -1090,308 +1090,308 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0105</v>
+        <v>3.1054</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7524</v>
+        <v>1.8077</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7462</v>
+        <v>0.7733</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0105</v>
+        <v>3.1054</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0105</v>
+        <v>2.9261</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8642</v>
+        <v>3.6794</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0659</v>
+        <v>3.6794</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.0659</v>
+        <v>3.6794</v>
       </c>
       <c r="N15" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9475</v>
+        <v>3.0985</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7157</v>
+        <v>1.8036</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7176</v>
+        <v>0.7702</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9475</v>
+        <v>3.0985</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9475</v>
+        <v>2.4669</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7263</v>
+        <v>2.6744</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9208</v>
+        <v>2.6744</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9208</v>
+        <v>2.6744</v>
       </c>
       <c r="N16" t="n">
-        <v>201</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9261</v>
+        <v>3.0473</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7033</v>
+        <v>1.7738</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7078</v>
+        <v>0.7473</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9261</v>
+        <v>3.0473</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9261</v>
+        <v>2.9475</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6794</v>
+        <v>3.7263</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6794</v>
+        <v>3.9208</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6794</v>
+        <v>3.9208</v>
       </c>
       <c r="N17" t="n">
-        <v>172</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.9051</v>
+        <v>3.021</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6911</v>
+        <v>1.7585</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6983</v>
+        <v>0.7356</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9051</v>
+        <v>3.021</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5634</v>
+        <v>3.0105</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6583</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8629</v>
+        <v>3.8642</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7059</v>
+        <v>4.0659</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6583</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="L18" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0476</v>
+        <v>4.0659</v>
       </c>
       <c r="N18" t="n">
-        <v>178</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6048</v>
+        <v>2.8984</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5163</v>
+        <v>1.6872</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5616</v>
+        <v>0.6808</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6048</v>
+        <v>2.8984</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5759</v>
+        <v>3.5634</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0289</v>
+        <v>-0.6583</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6047</v>
+        <v>6.8629</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9465</v>
+        <v>3.7059</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0289</v>
+        <v>-0.6583</v>
       </c>
       <c r="K19" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9754</v>
+        <v>3.0476</v>
       </c>
       <c r="N19" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5935</v>
+        <v>2.6935</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5097</v>
+        <v>1.5679</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5564</v>
+        <v>0.5893</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5935</v>
+        <v>2.6935</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5935</v>
+        <v>2.5759</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0289</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9515</v>
+        <v>3.6047</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9515</v>
+        <v>1.9465</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.0289</v>
       </c>
       <c r="K20" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9515</v>
+        <v>1.9754</v>
       </c>
       <c r="N20" t="n">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.499</v>
+        <v>2.6866</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4547</v>
+        <v>1.5639</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5134</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>2.499</v>
+        <v>2.6866</v>
       </c>
       <c r="F21" t="n">
-        <v>2.499</v>
+        <v>2.5935</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7446</v>
+        <v>2.9515</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7446</v>
+        <v>2.9515</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7446</v>
+        <v>2.9515</v>
       </c>
       <c r="N21" t="n">
         <v>172</v>
@@ -1412,170 +1412,170 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.4669</v>
+        <v>2.6768</v>
       </c>
       <c r="C22" t="n">
-        <v>1.436</v>
+        <v>1.5582</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4988</v>
+        <v>0.5818</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4669</v>
+        <v>2.6768</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4669</v>
+        <v>2.3958</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6744</v>
+        <v>2.5187</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6744</v>
+        <v>2.5187</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6744</v>
+        <v>2.5187</v>
       </c>
       <c r="N22" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.3958</v>
+        <v>2.3782</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3946</v>
+        <v>1.3844</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4664</v>
+        <v>0.4485</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3958</v>
+        <v>2.3782</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3958</v>
+        <v>2.499</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5187</v>
+        <v>2.7446</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5187</v>
+        <v>2.7446</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5187</v>
+        <v>2.7446</v>
       </c>
       <c r="N23" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3367</v>
+        <v>2.3703</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3602</v>
+        <v>1.3798</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4395</v>
+        <v>0.4449</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3367</v>
+        <v>2.3703</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7233</v>
+        <v>2.2098</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3866</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.091</v>
+        <v>2.2098</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2091</v>
+        <v>2.2098</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3866</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8225</v>
+        <v>2.2098</v>
       </c>
       <c r="N24" t="n">
-        <v>149</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.3052</v>
+        <v>2.356</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3419</v>
+        <v>1.3714</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4252</v>
+        <v>0.4386</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3052</v>
+        <v>2.356</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3052</v>
+        <v>2.0335</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3205</v>
+        <v>2.0335</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3205</v>
+        <v>2.0335</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.3205</v>
+        <v>2.0335</v>
       </c>
       <c r="N25" t="n">
         <v>145</v>
@@ -1596,415 +1596,415 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.2629</v>
+        <v>2.3135</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3172</v>
+        <v>1.3467</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4059</v>
+        <v>0.4196</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2629</v>
+        <v>2.3135</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4577</v>
+        <v>2.1202</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1948</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2147</v>
+        <v>2.1202</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7359</v>
+        <v>2.1202</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1948</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="L26" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5411</v>
+        <v>2.1202</v>
       </c>
       <c r="N26" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2312</v>
+        <v>2.3058</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2988</v>
+        <v>1.3422</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3915</v>
+        <v>0.4161</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2312</v>
+        <v>2.3058</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2312</v>
+        <v>2.7233</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3866</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2312</v>
+        <v>4.091</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2312</v>
+        <v>2.2091</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3866</v>
       </c>
       <c r="K27" t="n">
         <v>117</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M27" t="n">
-        <v>2.2312</v>
+        <v>1.8225</v>
       </c>
       <c r="N27" t="n">
-        <v>117</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2098</v>
+        <v>2.3054</v>
       </c>
       <c r="C28" t="n">
-        <v>1.2863</v>
+        <v>1.342</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3817</v>
+        <v>0.416</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2098</v>
+        <v>2.3054</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2098</v>
+        <v>2.177</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2098</v>
+        <v>2.177</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2098</v>
+        <v>2.2906</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2098</v>
+        <v>2.2906</v>
       </c>
       <c r="N28" t="n">
-        <v>123</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.1918</v>
+        <v>2.2867</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2759</v>
+        <v>1.3311</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3735</v>
+        <v>0.4076</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1918</v>
+        <v>2.2867</v>
       </c>
       <c r="F29" t="n">
-        <v>2.6127</v>
+        <v>2.3052</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4209</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9935</v>
+        <v>2.3205</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2309</v>
+        <v>2.3205</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4209</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="L29" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.81</v>
+        <v>2.3205</v>
       </c>
       <c r="N29" t="n">
-        <v>218</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.177</v>
+        <v>2.2402</v>
       </c>
       <c r="C30" t="n">
-        <v>1.2672</v>
+        <v>1.304</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3668</v>
+        <v>0.3868</v>
       </c>
       <c r="E30" t="n">
-        <v>2.177</v>
+        <v>2.2402</v>
       </c>
       <c r="F30" t="n">
-        <v>2.177</v>
+        <v>2.2312</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.177</v>
+        <v>2.2312</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2906</v>
+        <v>2.2312</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.2906</v>
+        <v>2.2312</v>
       </c>
       <c r="N30" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.1346</v>
+        <v>2.2235</v>
       </c>
       <c r="C31" t="n">
-        <v>1.2426</v>
+        <v>1.2943</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3475</v>
+        <v>0.3794</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1346</v>
+        <v>2.2235</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5914</v>
+        <v>2.4577</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4568</v>
+        <v>-0.1948</v>
       </c>
       <c r="H31" t="n">
-        <v>2.9469</v>
+        <v>3.2147</v>
       </c>
       <c r="I31" t="n">
-        <v>3.1806</v>
+        <v>1.7359</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4568</v>
+        <v>-0.1948</v>
       </c>
       <c r="K31" t="n">
-        <v>177</v>
+        <v>107</v>
       </c>
       <c r="L31" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="M31" t="n">
-        <v>2.7238</v>
+        <v>1.5411</v>
       </c>
       <c r="N31" t="n">
-        <v>218</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.1202</v>
+        <v>2.2191</v>
       </c>
       <c r="C32" t="n">
-        <v>1.2342</v>
+        <v>1.2917</v>
       </c>
       <c r="D32" t="n">
-        <v>0.341</v>
+        <v>0.3774</v>
       </c>
       <c r="E32" t="n">
-        <v>2.1202</v>
+        <v>2.2191</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1202</v>
+        <v>2.6127</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.4209</v>
       </c>
       <c r="H32" t="n">
-        <v>2.1202</v>
+        <v>2.9935</v>
       </c>
       <c r="I32" t="n">
-        <v>2.1202</v>
+        <v>3.2309</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.4209</v>
       </c>
       <c r="K32" t="n">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M32" t="n">
-        <v>2.1202</v>
+        <v>2.81</v>
       </c>
       <c r="N32" t="n">
-        <v>145</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.0335</v>
+        <v>2.1721</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1837</v>
+        <v>1.2644</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3015</v>
+        <v>0.3564</v>
       </c>
       <c r="E33" t="n">
-        <v>2.0335</v>
+        <v>2.1721</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0335</v>
+        <v>2.0305</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0335</v>
+        <v>2.0305</v>
       </c>
       <c r="I33" t="n">
-        <v>2.0335</v>
+        <v>2.0305</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.0335</v>
+        <v>2.0305</v>
       </c>
       <c r="N33" t="n">
-        <v>145</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.0305</v>
+        <v>2.0863</v>
       </c>
       <c r="C34" t="n">
-        <v>1.182</v>
+        <v>1.2144</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3001</v>
+        <v>0.3181</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0305</v>
+        <v>2.0863</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0305</v>
+        <v>2.5914</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.4568</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0305</v>
+        <v>2.9469</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0305</v>
+        <v>3.1806</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.4568</v>
       </c>
       <c r="K34" t="n">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M34" t="n">
-        <v>2.0305</v>
+        <v>2.7238</v>
       </c>
       <c r="N34" t="n">
-        <v>113</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.8703</v>
+        <v>1.9914</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0887</v>
+        <v>1.1592</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2272</v>
+        <v>0.2757</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8703</v>
+        <v>1.9914</v>
       </c>
       <c r="F35" t="n">
         <v>1.8703</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.7918</v>
+        <v>1.8504</v>
       </c>
       <c r="C36" t="n">
-        <v>1.043</v>
+        <v>1.0771</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1915</v>
+        <v>0.2127</v>
       </c>
       <c r="E36" t="n">
-        <v>1.7918</v>
+        <v>1.8504</v>
       </c>
       <c r="F36" t="n">
         <v>1.7918</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.7162</v>
+        <v>1.8339</v>
       </c>
       <c r="C37" t="n">
-        <v>0.999</v>
+        <v>1.0675</v>
       </c>
       <c r="D37" t="n">
-        <v>0.157</v>
+        <v>0.2053</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7162</v>
+        <v>1.8339</v>
       </c>
       <c r="F37" t="n">
-        <v>1.7162</v>
+        <v>1.6511</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.7162</v>
+        <v>1.6511</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7162</v>
+        <v>1.6511</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.7162</v>
+        <v>1.6511</v>
       </c>
       <c r="N37" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6814</v>
+        <v>1.8189</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9787</v>
+        <v>1.0588</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1412</v>
+        <v>0.1986</v>
       </c>
       <c r="E38" t="n">
-        <v>1.6814</v>
+        <v>1.8189</v>
       </c>
       <c r="F38" t="n">
         <v>1.6814</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.6744</v>
+        <v>1.7459</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9747</v>
+        <v>1.0163</v>
       </c>
       <c r="D39" t="n">
-        <v>0.138</v>
+        <v>0.166</v>
       </c>
       <c r="E39" t="n">
-        <v>1.6744</v>
+        <v>1.7459</v>
       </c>
       <c r="F39" t="n">
         <v>1.6744</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.6511</v>
+        <v>1.7101</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9611</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1274</v>
+        <v>0.15</v>
       </c>
       <c r="E40" t="n">
-        <v>1.6511</v>
+        <v>1.7101</v>
       </c>
       <c r="F40" t="n">
-        <v>1.6511</v>
+        <v>1.7162</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.6511</v>
+        <v>1.7162</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6511</v>
+        <v>1.7162</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.6511</v>
+        <v>1.7162</v>
       </c>
       <c r="N40" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3256</v>
+        <v>1.4603</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7716</v>
+        <v>0.85</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0208</v>
+        <v>0.0385</v>
       </c>
       <c r="E41" t="n">
-        <v>1.3256</v>
+        <v>1.4603</v>
       </c>
       <c r="F41" t="n">
         <v>1.3256</v>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3078</v>
+        <v>1.2833</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7613</v>
+        <v>0.747</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0289</v>
+        <v>-0.0406</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3078</v>
+        <v>1.2833</v>
       </c>
       <c r="F42" t="n">
         <v>1.166</v>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.3022</v>
+        <v>1.2325</v>
       </c>
       <c r="C43" t="n">
-        <v>0.758</v>
+        <v>0.7174</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0314</v>
+        <v>-0.0633</v>
       </c>
       <c r="E43" t="n">
-        <v>1.3022</v>
+        <v>1.2325</v>
       </c>
       <c r="F43" t="n">
         <v>1.83</v>
@@ -2424,124 +2424,124 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1563</v>
+        <v>1.2298</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6731</v>
+        <v>0.7159</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0978</v>
+        <v>-0.0645</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1563</v>
+        <v>1.2298</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7572</v>
+        <v>0.85</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3991</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7572</v>
+        <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7572</v>
+        <v>0.85</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3991</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="L44" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1563</v>
+        <v>0.85</v>
       </c>
       <c r="N44" t="n">
-        <v>182</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8908</v>
+        <v>1.1007</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5185</v>
+        <v>0.6407</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2187</v>
+        <v>-0.1222</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8908</v>
+        <v>1.1007</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3864</v>
+        <v>0.7572</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.4956</v>
+        <v>0.3991</v>
       </c>
       <c r="H45" t="n">
-        <v>1.3864</v>
+        <v>0.7572</v>
       </c>
       <c r="I45" t="n">
-        <v>1.4964</v>
+        <v>0.7572</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.4956</v>
+        <v>0.3991</v>
       </c>
       <c r="K45" t="n">
-        <v>177</v>
+        <v>115</v>
       </c>
       <c r="L45" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="M45" t="n">
-        <v>1.0008</v>
+        <v>1.1563</v>
       </c>
       <c r="N45" t="n">
-        <v>218</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.85</v>
+        <v>0.8946</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4948</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2373</v>
+        <v>-0.2142</v>
       </c>
       <c r="E46" t="n">
-        <v>0.85</v>
+        <v>0.8946</v>
       </c>
       <c r="F46" t="n">
-        <v>0.85</v>
+        <v>0.7448</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.85</v>
+        <v>0.7448</v>
       </c>
       <c r="I46" t="n">
-        <v>0.85</v>
+        <v>0.7448</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.85</v>
+        <v>0.7448</v>
       </c>
       <c r="N46" t="n">
         <v>74</v>
@@ -2562,369 +2562,369 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8413</v>
+        <v>0.8829</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4897</v>
+        <v>0.5139</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2412</v>
+        <v>-0.2194</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8413</v>
+        <v>0.8829</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7631</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.07820000000000001</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7631</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8236</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07820000000000001</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="L47" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.9018</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>218</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8134</v>
+        <v>0.8247</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4735</v>
+        <v>0.4801</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2539</v>
+        <v>-0.2454</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8134</v>
+        <v>0.8247</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1413</v>
+        <v>1.3864</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6721</v>
+        <v>-0.4956</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1413</v>
+        <v>1.3864</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1413</v>
+        <v>1.4964</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6721</v>
+        <v>-0.4956</v>
       </c>
       <c r="K48" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="L48" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8134</v>
+        <v>1.0008</v>
       </c>
       <c r="N48" t="n">
-        <v>182</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7448</v>
+        <v>0.8011</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4336</v>
+        <v>0.4663</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2852</v>
+        <v>-0.256</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7448</v>
+        <v>0.8011</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7448</v>
+        <v>0.7631</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7448</v>
+        <v>0.7631</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7448</v>
+        <v>0.8236</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7448</v>
+        <v>0.9018</v>
       </c>
       <c r="N49" t="n">
-        <v>74</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.73</v>
+        <v>0.6898</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4249</v>
+        <v>0.4015</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2919</v>
+        <v>-0.3057</v>
       </c>
       <c r="E50" t="n">
-        <v>0.73</v>
+        <v>0.6898</v>
       </c>
       <c r="F50" t="n">
-        <v>0.73</v>
+        <v>0.1413</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.6721</v>
       </c>
       <c r="H50" t="n">
-        <v>0.73</v>
+        <v>0.1413</v>
       </c>
       <c r="I50" t="n">
-        <v>0.73</v>
+        <v>0.1413</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.6721</v>
       </c>
       <c r="K50" t="n">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M50" t="n">
-        <v>0.73</v>
+        <v>0.8134</v>
       </c>
       <c r="N50" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5686</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3964</v>
+        <v>0.331</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3142</v>
+        <v>-0.3598</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5686</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3336</v>
+        <v>0.3195</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3633</v>
+        <v>-0.3686</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="N52" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4923</v>
+        <v>0.4784</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2866</v>
+        <v>0.2785</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4001</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4923</v>
+        <v>0.4784</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4923</v>
+        <v>0.2944</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4923</v>
+        <v>0.2944</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4923</v>
+        <v>0.2944</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4923</v>
+        <v>0.2944</v>
       </c>
       <c r="N53" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2944</v>
+        <v>0.401</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1714</v>
+        <v>0.2334</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4902</v>
+        <v>-0.4347</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2944</v>
+        <v>0.401</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2944</v>
+        <v>0.4923</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2944</v>
+        <v>0.4923</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2944</v>
+        <v>0.4923</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2944</v>
+        <v>0.4923</v>
       </c>
       <c r="N54" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2075</v>
+        <v>0.372</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1208</v>
+        <v>0.2165</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.4477</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2075</v>
+        <v>0.372</v>
       </c>
       <c r="F55" t="n">
         <v>0.2075</v>
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1286</v>
+        <v>-0.0435</v>
       </c>
       <c r="C56" t="n">
-        <v>0.07489999999999999</v>
+        <v>-0.0253</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5657</v>
+        <v>-0.6333</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1286</v>
+        <v>-0.0435</v>
       </c>
       <c r="F56" t="n">
         <v>0.1286</v>
@@ -3022,231 +3022,231 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0833</v>
+        <v>-0.0659</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0485</v>
+        <v>-0.0384</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5863</v>
+        <v>-0.6433</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0833</v>
+        <v>-0.0659</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0833</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.0511</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0833</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0833</v>
+        <v>-0.0047</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.0511</v>
       </c>
       <c r="K57" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0833</v>
+        <v>0.0464</v>
       </c>
       <c r="N57" t="n">
-        <v>96</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0424</v>
+        <v>-0.0694</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0247</v>
+        <v>-0.0404</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6049</v>
+        <v>-0.6448</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0424</v>
+        <v>-0.0694</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0511</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0047</v>
+        <v>0.0833</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0511</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="L58" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0464</v>
+        <v>0.0833</v>
       </c>
       <c r="N58" t="n">
-        <v>178</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.0978</v>
+        <v>-0.1018</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0569</v>
+        <v>-0.0593</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6687</v>
+        <v>-0.6593</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0978</v>
+        <v>-0.1018</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0978</v>
+        <v>-0.1589</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0978</v>
+        <v>-0.1589</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0978</v>
+        <v>-0.1589</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.0978</v>
+        <v>-0.1589</v>
       </c>
       <c r="N59" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1135</v>
+        <v>-0.19</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.1106</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6987</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1135</v>
+        <v>-0.19</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0117</v>
+        <v>-0.0978</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.1252</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0117</v>
+        <v>-0.0978</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0117</v>
+        <v>-0.0978</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.1252</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="L60" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1135</v>
+        <v>-0.0978</v>
       </c>
       <c r="N60" t="n">
-        <v>308</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1589</v>
+        <v>-0.3176</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0925</v>
+        <v>-0.1849</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6965</v>
+        <v>-0.7557</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1589</v>
+        <v>-0.3176</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1589</v>
+        <v>0.0117</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-0.1252</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1589</v>
+        <v>0.0117</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1589</v>
+        <v>0.0117</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-0.1252</v>
       </c>
       <c r="K61" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.1589</v>
+        <v>-0.1135</v>
       </c>
       <c r="N61" t="n">
-        <v>85</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62">
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1986</v>
+        <v>-0.3344</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1156</v>
+        <v>-0.1947</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7146</v>
+        <v>-0.7632</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1986</v>
+        <v>-0.3344</v>
       </c>
       <c r="F62" t="n">
         <v>0.7715</v>
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3612</v>
+        <v>-0.4818</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2103</v>
+        <v>-0.2805</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7886</v>
+        <v>-0.829</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3612</v>
+        <v>-0.4818</v>
       </c>
       <c r="F63" t="n">
         <v>-0.3612</v>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4419</v>
+        <v>-0.547</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2572</v>
+        <v>-0.3184</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8254</v>
+        <v>-0.8582</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4419</v>
+        <v>-0.547</v>
       </c>
       <c r="F64" t="n">
         <v>-0.4419</v>
@@ -3390,461 +3390,461 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6808</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3348</v>
+        <v>-0.3963</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.886</v>
+        <v>-0.9179</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6808</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6462</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6462</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6462</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6462</v>
       </c>
       <c r="N65" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6462</v>
+        <v>-0.7372</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3762</v>
+        <v>-0.4291</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9184</v>
+        <v>-0.9431</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6462</v>
+        <v>-0.7372</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6462</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6462</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6462</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6462</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7491</v>
+        <v>-0.8593</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4361</v>
+        <v>-0.5002</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.9977</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7491</v>
+        <v>-0.8593</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7491</v>
+        <v>-0.8424</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7491</v>
+        <v>-0.8424</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7491</v>
+        <v>-0.8424</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7491</v>
+        <v>-0.8424</v>
       </c>
       <c r="N67" t="n">
-        <v>145</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8354</v>
+        <v>-0.9422</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4863</v>
+        <v>-0.5485</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0045</v>
+        <v>-1.0347</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8354</v>
+        <v>-0.9422</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8354</v>
+        <v>-0.7491</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8354</v>
+        <v>-0.7491</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8354</v>
+        <v>-0.7491</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8354</v>
+        <v>-0.7491</v>
       </c>
       <c r="N68" t="n">
-        <v>59</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8424</v>
+        <v>-1.0821</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4904</v>
+        <v>-0.6299</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0077</v>
+        <v>-1.0972</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8424</v>
+        <v>-1.0821</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8424</v>
+        <v>-0.4075</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8424</v>
+        <v>-0.4075</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8424</v>
+        <v>-0.4075</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8424</v>
+        <v>-0.9099999999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>96</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.91</v>
+        <v>-1.1091</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.6456</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0385</v>
+        <v>-1.1092</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.91</v>
+        <v>-1.1091</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.4075</v>
+        <v>-0.8354</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.5024999999999999</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.4075</v>
+        <v>-0.8354</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4075</v>
+        <v>-0.8354</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5024999999999999</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="L70" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9099999999999999</v>
+        <v>-0.8354</v>
       </c>
       <c r="N70" t="n">
-        <v>182</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9523</v>
+        <v>-1.1532</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5543</v>
+        <v>-0.6713</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0577</v>
+        <v>-1.1289</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9523</v>
+        <v>-1.1532</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9523</v>
+        <v>-1.0982</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9523</v>
+        <v>-1.0982</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9523</v>
+        <v>-1.0982</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9523</v>
+        <v>-1.0982</v>
       </c>
       <c r="N71" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0982</v>
+        <v>-1.342</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6393</v>
+        <v>-0.7812</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1241</v>
+        <v>-1.2133</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0982</v>
+        <v>-1.342</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0982</v>
+        <v>-0.9523</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0982</v>
+        <v>-0.9523</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0982</v>
+        <v>-0.9523</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.0982</v>
+        <v>-0.9523</v>
       </c>
       <c r="N72" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2901</v>
+        <v>-1.5014</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.751</v>
+        <v>-0.874</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2115</v>
+        <v>-1.2845</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2901</v>
+        <v>-1.5014</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2901</v>
+        <v>-1.3489</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2901</v>
+        <v>-1.3489</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2901</v>
+        <v>-1.3489</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.2901</v>
+        <v>-1.3489</v>
       </c>
       <c r="N73" t="n">
-        <v>59</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3489</v>
+        <v>-1.8323</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7852</v>
+        <v>-1.0666</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2383</v>
+        <v>-1.4323</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3489</v>
+        <v>-1.8323</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3489</v>
+        <v>-1.2901</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3489</v>
+        <v>-1.2901</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.3489</v>
+        <v>-1.2901</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.3489</v>
+        <v>-1.2901</v>
       </c>
       <c r="N74" t="n">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75">
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.4019</v>
+        <v>-1.8331</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8161</v>
+        <v>-1.0671</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2624</v>
+        <v>-1.4326</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.4019</v>
+        <v>-1.8331</v>
       </c>
       <c r="F75" t="n">
         <v>-1.4019</v>
@@ -3896,124 +3896,124 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.4258</v>
+        <v>-1.8581</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.83</v>
+        <v>-1.0816</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2733</v>
+        <v>-1.4438</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.4258</v>
+        <v>-1.8581</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.4258</v>
+        <v>-1.714</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.4258</v>
+        <v>-1.714</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.4258</v>
+        <v>-1.714</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.4258</v>
+        <v>-1.714</v>
       </c>
       <c r="N76" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6536</v>
+        <v>-1.9396</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9626</v>
+        <v>-1.129</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.377</v>
+        <v>-1.4802</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6536</v>
+        <v>-1.9396</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.6536</v>
+        <v>-1.4258</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.6536</v>
+        <v>-1.4258</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.6536</v>
+        <v>-1.4258</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.6536</v>
+        <v>-1.4258</v>
       </c>
       <c r="N77" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.714</v>
+        <v>-2.1323</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.9977</v>
+        <v>-1.2412</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4045</v>
+        <v>-1.5663</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.714</v>
+        <v>-2.1323</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.714</v>
+        <v>-1.6536</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.714</v>
+        <v>-1.6536</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.714</v>
+        <v>-1.6536</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.714</v>
+        <v>-1.6536</v>
       </c>
       <c r="N78" t="n">
         <v>123</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.0496</v>
+        <v>-2.1428</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1931</v>
+        <v>-1.2473</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5572</v>
+        <v>-1.571</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.0496</v>
+        <v>-2.1428</v>
       </c>
       <c r="F79" t="n">
         <v>-2.0496</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.4639</v>
+        <v>-2.6363</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.4342</v>
+        <v>-1.5346</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7458</v>
+        <v>-1.7914</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.4639</v>
+        <v>-2.6363</v>
       </c>
       <c r="F80" t="n">
         <v>-2.4639</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.1335</v>
+        <v>-3.2458</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.824</v>
+        <v>-1.8894</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0506</v>
+        <v>-2.0636</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.1335</v>
+        <v>-3.2458</v>
       </c>
       <c r="F81" t="n">
         <v>-1.3136</v>
